--- a/train2.xlsx
+++ b/train2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ChatbotPerpusBipa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7463872-7346-4B39-8D87-7A1A7D173AEC}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BB3459-141F-4F24-A7AB-AEE7D99EEAAF}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Book1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Book1!$A$1002:$A$1012</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Book1!$A$1:$B$1489</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2978" uniqueCount="1450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3002" uniqueCount="1462">
   <si>
     <t>text</t>
   </si>
@@ -4380,6 +4380,42 @@
   </si>
   <si>
     <t>siang kak tolong info tata tertib lengkap perpustakaan dong makasih</t>
+  </si>
+  <si>
+    <t>Saya boleh masuk perpus tidak sekarang?</t>
+  </si>
+  <si>
+    <t>selamat sore, jadwal besok apakah dibuka perpus bipa?</t>
+  </si>
+  <si>
+    <t>oke boleh aku setuju</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yaudah gitu aja </t>
+  </si>
+  <si>
+    <t>boleh sekali ya</t>
+  </si>
+  <si>
+    <t>iyaaaaaaaaaaa</t>
+  </si>
+  <si>
+    <t>kamu mengerti</t>
+  </si>
+  <si>
+    <t>apa kabar teman!</t>
+  </si>
+  <si>
+    <t>saya ingin mencoba ini</t>
+  </si>
+  <si>
+    <t>cek cek cek</t>
+  </si>
+  <si>
+    <t>p bantu saya boleh?</t>
+  </si>
+  <si>
+    <t>initiate</t>
   </si>
 </sst>
 </file>
@@ -5226,7 +5262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1489"/>
+  <dimension ref="A1:C1501"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="100.28515625" bestFit="1" customWidth="1"/>
@@ -17153,6 +17189,102 @@
         <v>1127</v>
       </c>
     </row>
+    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1490" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B1490" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1491" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B1491" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1492" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B1492" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1493" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B1493" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1494" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B1494" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1495" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B1495" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1496" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B1496" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1497" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B1497" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1498" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B1498" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1499" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B1499" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1500" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B1500" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1501" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B1501" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="C67:C165">
     <sortCondition ref="C67:C165"/>
